--- a/05_Bases_de_Datos/02_Ejercicios_Normalizacion/Ejercicios de Normalización.xlsx
+++ b/05_Bases_de_Datos/02_Ejercicios_Normalizacion/Ejercicios de Normalización.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\epied\Downloads\Lyfter\Teoría_Lyfter\06_Bases de Datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\epied\Downloads\Lyfter\Ejercicios_Lyfter\05_Bases_de_Datos\02_Ejercicios_Normalizacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9E5C1E-8E66-48A9-BE36-433717AF4F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4804B64D-6CF8-4C25-B698-0BC65029F6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,8 +17,8 @@
     <sheet name="Ejercicio Cars" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Ejercicio Cars'!$A$1:$J$143</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Ejercicio Orders'!$A$1:$J$94</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Ejercicio Cars'!$A$1:$J$38,'Ejercicio Cars'!$A$39:$H$124,'Ejercicio Cars'!$A$125:$D$140</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Ejercicio Orders'!$A$1:$J$93</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="156">
   <si>
     <t>Order ID</t>
   </si>
@@ -398,9 +398,6 @@
     <t>Tabla Insurance_Companies</t>
   </si>
   <si>
-    <t>Insurance Company ID</t>
-  </si>
-  <si>
     <t>Tabla Owners</t>
   </si>
   <si>
@@ -413,9 +410,6 @@
     <t>En la tabla Insurance_Companies, las políticas no dependen directamente de la empresa. De hecho una empresa puede tener diferentes políticas,</t>
   </si>
   <si>
-    <t>Además, en la tabla Models, el fabricante no se identifica por el modelo, el color tampoco depende del modelo</t>
-  </si>
-  <si>
     <t>Tabla Insurance_Policies</t>
   </si>
   <si>
@@ -425,18 +419,12 @@
     <t>Policy</t>
   </si>
   <si>
-    <t>Insurance Policy ID</t>
-  </si>
-  <si>
     <t>Make ID</t>
   </si>
   <si>
     <t>Tabla Makes</t>
   </si>
   <si>
-    <t>Entonces se crean las tablas Makes y Colors</t>
-  </si>
-  <si>
     <t>Tabla Colors</t>
   </si>
   <si>
@@ -467,9 +455,6 @@
     <t>104</t>
   </si>
   <si>
-    <t>En la tabla Vehicles, la clave primaria no identifica de manera única a la información relacionada con Color, Year, Make y Model</t>
-  </si>
-  <si>
     <t>En la tabla Owners, la clave primaria no identifica de manera única a la información relacionada a la aseguradora</t>
   </si>
   <si>
@@ -485,9 +470,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t xml:space="preserve">por eso es más apropiado regresar Insurance Policy a la tabla Owners, para relacionar cada persona con una política, y se crea la tabla Insurance_Policies </t>
-  </si>
-  <si>
     <t>Talba Vehicles</t>
   </si>
   <si>
@@ -498,6 +480,24 @@
   </si>
   <si>
     <t>Ejercicio Orders</t>
+  </si>
+  <si>
+    <t>En la tabla Vehicles, la clave primaria no identifica de manera única a la información relacionada con Year, Make y Model</t>
+  </si>
+  <si>
+    <t>Además, un vehículo puede tener diferentes políticas aplicadas, de diferentes empresas.</t>
+  </si>
+  <si>
+    <t>Además, en la tabla Models, el fabricante no se identifica por el modelo. El color tampoco depende del modelo, en realidad depende de cada carro</t>
+  </si>
+  <si>
+    <t>Entonces se crean la tabla Insurance_Policies y la tabla Vehicle-Policy-Company, para relacionar toda la información</t>
+  </si>
+  <si>
+    <t>Entonces se crean las tablas Makes y Colors. La columna de color vuelve a formar parte de la tabla Vehicles</t>
+  </si>
+  <si>
+    <t>Tabla Vehicle-Policy-Company</t>
   </si>
 </sst>
 </file>
@@ -570,7 +570,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -588,17 +588,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -606,61 +597,29 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -965,11 +924,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
-        <v>155</v>
-      </c>
-      <c r="J1" s="35" t="s">
-        <v>154</v>
+      <c r="A1" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -999,13 +958,13 @@
       <c r="G4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="6" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1031,13 +990,13 @@
       <c r="G5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="7">
         <v>2</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="7" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1063,13 +1022,13 @@
       <c r="G6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <v>1</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="7" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1095,13 +1054,13 @@
       <c r="G7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="7">
         <v>1</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="7" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1127,13 +1086,13 @@
       <c r="G8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="7">
         <v>2</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="7" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1159,13 +1118,13 @@
       <c r="G9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="7">
         <v>1</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="7" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1191,13 +1150,13 @@
       <c r="G10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="7">
         <v>1</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="7" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1211,7 +1170,7 @@
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="10" t="s">
         <v>80</v>
       </c>
       <c r="B12" s="2"/>
@@ -1222,7 +1181,7 @@
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="8" t="s">
         <v>82</v>
       </c>
       <c r="B13" s="2"/>
@@ -1232,91 +1191,91 @@
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="9" t="s">
         <v>87</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="12"/>
+      <c r="F14" s="9"/>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="9" t="s">
         <v>88</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="11"/>
+      <c r="F15" s="8"/>
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="12"/>
+      <c r="A16" s="9"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="20"/>
+      <c r="F16" s="1"/>
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="9" t="s">
         <v>100</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="20"/>
+      <c r="F17" s="1"/>
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="12"/>
+      <c r="A18" s="9"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="20"/>
+      <c r="F18" s="1"/>
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="9" t="s">
         <v>95</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="20"/>
+      <c r="F19" s="1"/>
       <c r="G19" s="2"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="9" t="s">
         <v>96</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="20"/>
+      <c r="F20" s="1"/>
       <c r="G20" s="2"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="9" t="s">
         <v>101</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="20"/>
+      <c r="F21" s="1"/>
       <c r="G21" s="2"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
+      <c r="A22" s="9"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -1325,7 +1284,7 @@
       <c r="G22" s="2"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="9" t="s">
         <v>81</v>
       </c>
       <c r="B23" s="2"/>
@@ -1345,7 +1304,7 @@
       <c r="C24" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="6" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1359,7 +1318,7 @@
       <c r="C25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1373,7 +1332,7 @@
       <c r="C26" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="7" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1387,7 +1346,7 @@
       <c r="C27" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="7" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1401,7 +1360,7 @@
       <c r="C28" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="7" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1409,7 +1368,7 @@
       <c r="A29"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="9" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1488,19 +1447,19 @@
       <c r="A39" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F39" s="17" t="s">
+      <c r="F39" s="5" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1514,10 +1473,10 @@
       <c r="C40" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D40" s="9" t="s">
+      <c r="D40" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E40" s="8">
+      <c r="E40" s="7">
         <v>2</v>
       </c>
       <c r="F40" s="3" t="s">
@@ -1534,10 +1493,10 @@
       <c r="C41" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D41" s="9" t="s">
+      <c r="D41" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E41" s="8">
+      <c r="E41" s="7">
         <v>1</v>
       </c>
       <c r="F41" s="3" t="s">
@@ -1554,10 +1513,10 @@
       <c r="C42" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D42" s="9" t="s">
+      <c r="D42" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E42" s="8">
+      <c r="E42" s="7">
         <v>1</v>
       </c>
       <c r="F42" s="3" t="s">
@@ -1574,10 +1533,10 @@
       <c r="C43" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="9" t="s">
+      <c r="D43" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E43" s="8">
+      <c r="E43" s="7">
         <v>2</v>
       </c>
       <c r="F43" s="3" t="s">
@@ -1594,10 +1553,10 @@
       <c r="C44" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D44" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E44" s="8">
+      <c r="E44" s="7">
         <v>1</v>
       </c>
       <c r="F44" s="3" t="s">
@@ -1605,19 +1564,19 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="7" t="s">
         <v>10</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E45" s="8">
+      <c r="E45" s="7">
         <v>1</v>
       </c>
       <c r="F45" s="3" t="s">
@@ -1625,17 +1584,17 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="8" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="9" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1701,7 +1660,7 @@
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="s">
+      <c r="A64" s="9" t="s">
         <v>81</v>
       </c>
       <c r="B64" s="2"/>
@@ -1715,13 +1674,13 @@
       <c r="A65" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="21" t="s">
+      <c r="B65" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="D65" s="6" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1729,13 +1688,13 @@
       <c r="A66" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D66" s="8" t="s">
+      <c r="D66" s="7" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1743,13 +1702,13 @@
       <c r="A67" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="D67" s="7" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1757,13 +1716,13 @@
       <c r="A68" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D68" s="8" t="s">
+      <c r="D68" s="7" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1771,13 +1730,13 @@
       <c r="A69" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="D69" s="7" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1785,13 +1744,13 @@
       <c r="A70" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D70" s="8" t="s">
+      <c r="D70" s="7" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1799,12 +1758,12 @@
       <c r="A71"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="14" t="s">
+      <c r="A72" s="9" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="19" t="s">
+      <c r="A73" s="11" t="s">
         <v>108</v>
       </c>
       <c r="B73" s="6" t="s">
@@ -1815,7 +1774,7 @@
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="9" t="s">
+      <c r="A74" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B74" s="3" t="s">
@@ -1826,7 +1785,7 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="9" t="s">
+      <c r="A75" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B75" s="3" t="s">
@@ -1837,7 +1796,7 @@
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="9" t="s">
+      <c r="A76" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B76" s="3" t="s">
@@ -1851,7 +1810,7 @@
       <c r="A77"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="14" t="s">
+      <c r="A78" s="9" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1930,16 +1889,16 @@
       <c r="A87" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B87" s="17" t="s">
+      <c r="B87" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C87" s="17" t="s">
+      <c r="C87" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D87" s="17" t="s">
+      <c r="D87" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E87" s="7" t="s">
+      <c r="E87" s="6" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1953,10 +1912,10 @@
       <c r="C88" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D88" s="9" t="s">
+      <c r="D88" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E88" s="8">
+      <c r="E88" s="7">
         <v>2</v>
       </c>
     </row>
@@ -1970,10 +1929,10 @@
       <c r="C89" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D89" s="9" t="s">
+      <c r="D89" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="8">
+      <c r="E89" s="7">
         <v>1</v>
       </c>
     </row>
@@ -1987,10 +1946,10 @@
       <c r="C90" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D90" s="9" t="s">
+      <c r="D90" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E90" s="8">
+      <c r="E90" s="7">
         <v>1</v>
       </c>
     </row>
@@ -2004,10 +1963,10 @@
       <c r="C91" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D91" s="9" t="s">
+      <c r="D91" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E91" s="8">
+      <c r="E91" s="7">
         <v>2</v>
       </c>
     </row>
@@ -2021,27 +1980,27 @@
       <c r="C92" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D92" s="9" t="s">
+      <c r="D92" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E92" s="8">
+      <c r="E92" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="8" t="s">
+      <c r="A93" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="B93" s="7" t="s">
         <v>93</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D93" s="9" t="s">
+      <c r="D93" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E93" s="8">
+      <c r="E93" s="7">
         <v>1</v>
       </c>
     </row>
@@ -2050,7 +2009,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="67" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="46" max="9" man="1"/>
+    <brk id="46" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -2060,30 +2019,30 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J143"/>
+  <dimension ref="A1:J140"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
     <col min="2" max="3" width="15.42578125" customWidth="1"/>
-    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="13.85546875" customWidth="1"/>
-    <col min="9" max="9" width="21" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" customWidth="1"/>
+    <col min="9" max="9" width="18.5703125" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="J1" s="35" t="s">
-        <v>154</v>
+      <c r="A1" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -2108,13 +2067,13 @@
       <c r="G4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="6" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2140,13 +2099,13 @@
       <c r="G5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="4" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2172,13 +2131,13 @@
       <c r="G6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="4" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2204,13 +2163,13 @@
       <c r="G7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="4" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2236,18 +2195,18 @@
       <c r="G8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="4" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="10" t="s">
         <v>80</v>
       </c>
       <c r="B10" s="2"/>
@@ -2256,7 +2215,7 @@
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="8" t="s">
         <v>82</v>
       </c>
       <c r="B11" s="2"/>
@@ -2265,7 +2224,7 @@
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="9" t="s">
         <v>87</v>
       </c>
       <c r="B12" s="2"/>
@@ -2274,7 +2233,7 @@
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="9" t="s">
         <v>88</v>
       </c>
       <c r="B13" s="2"/>
@@ -2283,32 +2242,31 @@
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="22"/>
+      <c r="A14" s="13"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
+      <c r="A15" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>142</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>37</v>
@@ -2325,13 +2283,9 @@
       <c r="F20" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20"/>
-    </row>
-    <row r="21" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="31" t="s">
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -2349,13 +2303,9 @@
       <c r="F21" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G21"/>
-      <c r="H21"/>
-      <c r="I21"/>
-      <c r="J21"/>
-    </row>
-    <row r="22" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="31" t="s">
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -2373,13 +2323,9 @@
       <c r="F22" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G22"/>
-      <c r="H22"/>
-      <c r="I22"/>
-      <c r="J22"/>
-    </row>
-    <row r="23" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="31" t="s">
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -2397,210 +2343,204 @@
       <c r="F23" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G23"/>
-      <c r="H23"/>
-      <c r="I23"/>
-      <c r="J23"/>
-    </row>
-    <row r="24" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="29"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-    </row>
-    <row r="25" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="B25"/>
-      <c r="C25"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-    </row>
-    <row r="26" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>42</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-    </row>
-    <row r="27" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>101</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-    </row>
-    <row r="28" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>102</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>103</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>104</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="4" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="29"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="30" t="s">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="14"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="7">
+        <v>1</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="7">
+        <v>2</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="7">
+        <v>3</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="7">
+        <v>4</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="C33" s="18" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" s="31">
-        <v>1</v>
-      </c>
-      <c r="B34" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="31" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" s="31">
-        <v>2</v>
-      </c>
-      <c r="B35" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" s="31">
-        <v>3</v>
-      </c>
-      <c r="B36" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="31" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" s="31">
-        <v>4</v>
-      </c>
-      <c r="B37" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="31" t="s">
-        <v>144</v>
-      </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="29"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
+      <c r="A38" s="14"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" s="32" t="s">
+      <c r="A39" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
@@ -2608,884 +2548,916 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="8" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="13" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" s="12" t="s">
-        <v>149</v>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>146</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>147</v>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>139</v>
+      <c r="A52" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C53" s="21" t="s">
-        <v>125</v>
+      <c r="A53" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="31" t="s">
-        <v>7</v>
+      <c r="A54" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>8</v>
+        <v>46</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>9</v>
+      <c r="A56" s="15" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="24" t="s">
-        <v>123</v>
+      <c r="A58" s="4">
+        <v>101</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>122</v>
+      <c r="A59" s="4">
+        <v>102</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" s="4">
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D60" s="10">
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D60" s="4">
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D61" s="10">
+        <v>55</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D61" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="14"/>
+      <c r="B62" s="14"/>
+      <c r="C62" s="14"/>
+      <c r="D62" s="14"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="B63" s="14"/>
+      <c r="C63" s="14"/>
+      <c r="D63" s="14"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D64" s="14"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="7">
+        <v>1</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" s="14"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="4">
-        <v>103</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D62" s="10">
+      <c r="B66" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" s="14"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="4">
-        <v>104</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D63" s="10">
+      <c r="B67" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D67" s="14"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="7">
         <v>4</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="29"/>
-      <c r="B64" s="29"/>
-      <c r="C64" s="23"/>
-      <c r="D64" s="23"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="30" t="s">
+      <c r="B68" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B65" s="29"/>
-      <c r="C65" s="29"/>
-      <c r="D65" s="23"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B66" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="C66" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="D66" s="23"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="31">
-        <v>1</v>
-      </c>
-      <c r="B67" s="31" t="s">
+      <c r="D68" s="14"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="14"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="D70" s="14"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D71" s="14"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C67" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="D67" s="23"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="31">
-        <v>2</v>
-      </c>
-      <c r="B68" s="31" t="s">
+      <c r="B72" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D72" s="14"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D73" s="14"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D74" s="14"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="14"/>
+      <c r="B76" s="14"/>
+      <c r="C76" s="14"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C68" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="D68" s="23"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="31">
-        <v>3</v>
-      </c>
-      <c r="B69" s="31" t="s">
+      <c r="B79" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D79" s="4">
+        <v>2003</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C69" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D69" s="23"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="31">
-        <v>4</v>
-      </c>
-      <c r="B70" s="31" t="s">
+      <c r="B80" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D80" s="4">
+        <v>2014</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C70" s="31" t="s">
+      <c r="B81" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D81" s="4">
+        <v>2015</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="16" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="D70" s="23"/>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="33"/>
-      <c r="B71" s="33"/>
-      <c r="C71" s="33"/>
-      <c r="D71" s="23"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="D72" s="23"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="D73" s="23"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B74" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D74" s="23"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B75" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D75" s="23"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B76" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D76" s="23"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B77" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="23"/>
-      <c r="B78" s="23"/>
-      <c r="C78" s="23"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="18" t="s">
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
         <v>125</v>
       </c>
-      <c r="B80" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D81" s="4">
-        <v>2003</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D82" s="4">
-        <v>2014</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D83" s="4">
-        <v>2015</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="25" t="s">
-        <v>148</v>
-      </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="12" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>126</v>
+      <c r="A86" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>127</v>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>134</v>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>139</v>
+      <c r="A94" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C95" s="21" t="s">
-        <v>125</v>
+      <c r="A95" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="31" t="s">
+      <c r="A96" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="D98" s="15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B96" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C96" s="8" t="s">
+      <c r="B100" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D100" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="31" t="s">
+      <c r="E100" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B97" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C97" s="8" t="s">
+      <c r="B101" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D101" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="31" t="s">
+      <c r="E101" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B98" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C98" s="8" t="s">
+      <c r="B102" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D102" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="7" t="s">
+      <c r="E102" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="14"/>
+      <c r="B104" s="14"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="B105" s="14"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B106" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C106" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="D106" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="B101" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="10" t="s">
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B107" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B102" s="10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="10" t="s">
+      <c r="C107" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B103" s="10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="10" t="s">
+      <c r="D108" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C109" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B104" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="10" t="s">
+      <c r="D109" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C110" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B105" s="10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="23"/>
-      <c r="B106" s="23"/>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="24" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="B108" s="7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B109" s="10" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B110" s="10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B111" s="10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="10" t="s">
+      <c r="D110" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B112" s="10" t="s">
-        <v>79</v>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="15" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="24" t="s">
-        <v>123</v>
+      <c r="A114" s="4">
+        <v>101</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D115" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="E115" s="7" t="s">
-        <v>131</v>
+      <c r="A115" s="4">
+        <v>102</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C116" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D116" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="E116" s="26" t="s">
-        <v>7</v>
+        <v>26</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C117" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D117" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="14"/>
+      <c r="B118" s="14"/>
+      <c r="C118" s="14"/>
+      <c r="D118" s="2"/>
+      <c r="E118" s="2"/>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="B119" s="14"/>
+      <c r="C119" s="14"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="2"/>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B120" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C120" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D120" s="2"/>
+      <c r="E120" s="2"/>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="7">
+        <v>1</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D121" s="2"/>
+      <c r="E121" s="2"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="7">
+        <v>2</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="7">
+        <v>3</v>
+      </c>
+      <c r="B123" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E117" s="26" t="s">
+      <c r="C123" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D123" s="2"/>
+      <c r="E123" s="2"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="7">
+        <v>4</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="D124" s="2"/>
+      <c r="E124" s="2"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D127" s="3">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="4">
-        <v>103</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C118" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D118" s="26" t="s">
+      <c r="B128" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D128" s="3">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E118" s="26" t="s">
+      <c r="B129" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D129" s="3">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B132" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B137" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="4">
-        <v>104</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C119" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D119" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E119" s="26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="29"/>
-      <c r="B120" s="29"/>
-      <c r="C120" s="23"/>
-      <c r="D120" s="13"/>
-      <c r="E120" s="13"/>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="B121" s="29"/>
-      <c r="C121" s="29"/>
-      <c r="D121" s="13"/>
-      <c r="E121" s="13"/>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="B122" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="C122" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="D122" s="13"/>
-      <c r="E122" s="13"/>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="31">
-        <v>1</v>
-      </c>
-      <c r="B123" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="C123" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="D123" s="13"/>
-      <c r="E123" s="13"/>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="31">
-        <v>2</v>
-      </c>
-      <c r="B124" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="C124" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="D124" s="13"/>
-      <c r="E124" s="13"/>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="31">
-        <v>3</v>
-      </c>
-      <c r="B125" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="C125" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D125" s="13"/>
-      <c r="E125" s="13"/>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="31">
-        <v>4</v>
-      </c>
-      <c r="B126" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="C126" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="D126" s="13"/>
-      <c r="E126" s="13"/>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="29"/>
-      <c r="B127" s="29"/>
-      <c r="C127" s="23"/>
-      <c r="D127" s="13"/>
-      <c r="E127" s="13"/>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D129" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E129" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C130" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D130" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E130" s="3">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B131" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E131" s="3">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B132" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C132" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E132" s="3">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="27" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="B135" s="19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B136" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B137" s="8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" s="27" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="B140" s="19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B141" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B142" s="8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B143" s="8" t="s">
+      <c r="B140" s="7" t="s">
         <v>54</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="76" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="79" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="38" max="9" man="1"/>
-    <brk id="83" max="9" man="1"/>
-    <brk id="127" max="9" man="1"/>
+    <brk id="38" max="16383" man="1"/>
+    <brk id="81" max="16383" man="1"/>
+    <brk id="124" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>